--- a/tech3.xlsx
+++ b/tech3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD9B006-9AD4-4AC1-AE40-E42147343C03}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC624AC1-C177-413D-A9C1-942578AB0B98}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="1" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930" activeTab="2" xr2:uid="{D746D7D5-B0A8-4858-AD5A-93AA09E65399}"/>
   </bookViews>
   <sheets>
     <sheet name="id_tech" sheetId="2" r:id="rId1"/>
@@ -20,9 +20,10 @@
     <sheet name="conv_prod_impact" sheetId="5" r:id="rId5"/>
     <sheet name="sub_imp" sheetId="6" r:id="rId6"/>
     <sheet name="trans_cop_imp" sheetId="7" r:id="rId7"/>
+    <sheet name="use_cp" sheetId="8" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="45">
   <si>
     <t>HC</t>
   </si>
@@ -132,9 +133,6 @@
     <t>Fertilizer</t>
   </si>
   <si>
-    <t>Elec</t>
-  </si>
-  <si>
     <t>kgCO2/t</t>
   </si>
   <si>
@@ -159,7 +157,19 @@
     <t>MJ/t</t>
   </si>
   <si>
-    <t>Biomethane</t>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>kgCO2eq/kg</t>
+  </si>
+  <si>
+    <t>kgCO2eq/kWh</t>
+  </si>
+  <si>
+    <t>GHG_prod</t>
+  </si>
+  <si>
+    <t>GHG_use</t>
   </si>
 </sst>
 </file>
@@ -228,33 +238,47 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
+      <sheetName val="Waste_characteristics"/>
       <sheetName val="LCI"/>
+      <sheetName val="SP_mid"/>
+      <sheetName val="SP_end"/>
       <sheetName val="Parameters"/>
-      <sheetName val="Waste_characteristics"/>
+      <sheetName val="Feuil5"/>
+      <sheetName val="HC_end"/>
+      <sheetName val="HC_mid"/>
+      <sheetName val="IC_mid"/>
+      <sheetName val="IC_end"/>
+      <sheetName val="impact_process_end"/>
+      <sheetName val="impact_process_mid"/>
       <sheetName val="AD_a_end"/>
       <sheetName val="AD_a_mid"/>
-      <sheetName val="impact_process_mid"/>
-      <sheetName val="impact_process_end"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
         <row r="23">
           <cell r="E23">
-            <v>389.1220666666668</v>
+            <v>509.03089819946877</v>
           </cell>
         </row>
         <row r="24">
           <cell r="E24">
-            <v>1652.2721600000007</v>
+            <v>2161.4235062008215</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -772,7 +796,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97EEBB80-2ABA-4FB4-95B0-0A371702950F}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.453125" customWidth="1"/>
@@ -780,7 +804,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -850,13 +874,13 @@
       </c>
       <c r="D4">
         <f>[1]LCI!$E$24</f>
-        <v>1652.2721600000007</v>
+        <v>2161.4235062008215</v>
       </c>
       <c r="E4">
         <v>41</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -871,21 +895,13 @@
       </c>
       <c r="D5">
         <f>[1]LCI!$E$23</f>
-        <v>389.1220666666668</v>
+        <v>509.03089819946877</v>
       </c>
       <c r="E5">
         <v>29</v>
       </c>
       <c r="F5" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -903,7 +919,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s">
         <v>24</v>
@@ -954,7 +970,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -976,51 +992,63 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B44D246-4F1C-42C3-89B4-E352479F0DBF}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.1796875" customWidth="1"/>
+    <col min="2" max="3" width="12.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>31</v>
       </c>
       <c r="B2">
         <v>200</v>
       </c>
-      <c r="C2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C2">
+        <v>80</v>
+      </c>
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>26</v>
       </c>
       <c r="B3">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C3">
+        <v>96</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>30</v>
       </c>
-      <c r="C4" t="s">
-        <v>34</v>
+      <c r="C4">
+        <v>97</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1035,7 +1063,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1062,7 +1090,7 @@
       </c>
       <c r="B4">
         <f>(coproduct!D3*subs_ratio!C2*conv_prod_impact!B2)+(coproduct!D4*subs_ratio!D3*conv_prod_impact!B3)+(coproduct!E5*subs_ratio!E4*conv_prod_impact!B4)</f>
-        <v>28654.08240000001</v>
+        <v>36291.352593012321</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1100,7 +1128,7 @@
         <v>0.2</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1111,7 +1139,7 @@
         <v>0.2</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1122,7 +1150,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1133,7 +1161,75 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFE6F016-02DD-4060-8294-B81ED667E50B}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="16.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
